--- a/confirmation_forms/035_sisv_basketball_playing_confirmation--confirmation_forms.xlsx
+++ b/confirmation_forms/035_sisv_basketball_playing_confirmation--confirmation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>player_confirmation</t>
+          <t>player_confirmation_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>player_name</t>
+          <t>player_name_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>team_name</t>
+          <t>team_name_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>confirm_until_date</t>
+          <t>confirm_until_date_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>confirm until</t>
+          <t>Confirm Until Date 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>confirm_until_time</t>
+          <t>confirm_until_time_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>confirm until</t>
+          <t>Confirm Until Time 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>confirm_until_date</t>
+          <t>confirm_until_date_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>confirm until date</t>
+          <t>Confirm Until Date 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>confirm_until_time</t>
+          <t>confirm_until_time_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>confirm until time</t>
+          <t>Confirm Until Time 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>additional notes</t>
+          <t>Note 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>player_name_choices</t>
+          <t>player_name_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>player_name_choices</t>
+          <t>player_name_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1228,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>player_name_choices</t>
+          <t>player_name_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>team_name_choices</t>
+          <t>team_name_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>team_name_choices</t>
+          <t>team_name_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>team_name_choices</t>
+          <t>team_name_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
